--- a/datasets/Pre_Dataset_Small.xlsx
+++ b/datasets/Pre_Dataset_Small.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\other files\Никитины работы\Honors Track\!!!!! NEURAL NETWORK\WF OPTIMIZER\public\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23684638-BC3C-4474-BFD6-E8A9F9EF100F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C42AAB-AED3-4AFA-8B06-BEF7099FCF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="49368" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6480" yWindow="348" windowWidth="22980" windowHeight="24996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="62">
   <si>
     <t>Gen</t>
   </si>
@@ -220,9 +220,6 @@
   </si>
   <si>
     <t>7.Generation</t>
-  </si>
-  <si>
-    <t>z</t>
   </si>
 </sst>
 </file>
@@ -1472,7 +1469,7 @@
         <v>6735.2754553415261</v>
       </c>
       <c r="S13" s="2">
-        <v>6605.943024053412</v>
+        <v>6605.9430240534102</v>
       </c>
       <c r="T13" s="2">
         <v>8857954.5454545449</v>
@@ -1663,8 +1660,8 @@
       <c r="N16" s="2">
         <v>2150</v>
       </c>
-      <c r="O16" s="2" t="s">
-        <v>62</v>
+      <c r="O16" s="2">
+        <v>2150</v>
       </c>
       <c r="P16" s="2">
         <v>2500</v>
